--- a/docs/毛公仔打版與量產時間表_草案v0.5.xlsx
+++ b/docs/毛公仔打版與量產時間表_草案v0.5.xlsx
@@ -108,6 +108,15 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -115,15 +124,6 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -548,7 +548,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="40" customHeight="1">
+    <row r="5" ht="72" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
           <t>W1</t>
@@ -561,428 +561,436 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>回覆四個造型的打樣排期</t>
+          <t>收到全部造型後，回覆每個造型的打樣排期</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>交機芯規格；向電路板供應商詢價、追加樣板</t>
-        </is>
-      </c>
-      <c r="E5" s="6" t="inlineStr"/>
-      <c r="F5" s="5" t="inlineStr"/>
+          <t>定下全部 IP 造型交玩具廠（目前只交了馬會）；交機芯規格；向電路板供應商詢價、追加樣板</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>10/16 全部造型交工廠</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>馬會兩款、政協青年聯會版、AI Buddy（如 1/15 出貨）的造型圖（正、側、背面，尺寸，顏色）全部交到工廠；工廠回覆打樣排期</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="40" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>W2</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t>10/19–10/23</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="C6" s="8" t="inlineStr">
         <is>
           <t>機芯盒 3D 設計、第一版初樣</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="D6" s="8" t="inlineStr">
         <is>
           <t>審 3D 圖；決定電路板改不改；定好 App 和網頁的對接方式</t>
         </is>
       </c>
-      <c r="E6" s="6" t="inlineStr"/>
-      <c r="F6" s="5" t="inlineStr"/>
+      <c r="E6" s="9" t="inlineStr"/>
+      <c r="F6" s="8" t="inlineStr"/>
     </row>
     <row r="7" ht="56" customHeight="1">
-      <c r="A7" s="7" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>W3</t>
         </is>
       </c>
-      <c r="B7" s="7" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>10/26–10/30</t>
         </is>
       </c>
-      <c r="C7" s="8" t="inlineStr">
+      <c r="C7" s="5" t="inlineStr">
         <is>
           <t>寄出第一版樣品（每款 3 隻）</t>
         </is>
       </c>
-      <c r="D7" s="8" t="inlineStr">
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>裝板實測，給修改意見；電路板定案</t>
         </is>
       </c>
-      <c r="E7" s="9" t="inlineStr">
+      <c r="E7" s="6" t="inlineStr">
         <is>
           <t>10/30 第一版樣品測試</t>
         </is>
       </c>
-      <c r="F7" s="8" t="inlineStr">
+      <c r="F7" s="5" t="inlineStr">
         <is>
           <t>收音（1 米）、喇叭響度、按鍵、Wi-Fi、充電、跌落全部測過；修改意見已交工廠</t>
         </is>
       </c>
     </row>
     <row r="8" ht="40" customHeight="1">
-      <c r="A8" s="7" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>W4</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>11/2–11/6</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="5" t="inlineStr">
         <is>
           <t>第二版樣品；機芯盒開模；20 隻測試樣品</t>
         </is>
       </c>
-      <c r="D8" s="8" t="inlineStr">
+      <c r="D8" s="5" t="inlineStr">
         <is>
           <t>量產電路板下單；內部測試開始；App 開發</t>
         </is>
       </c>
-      <c r="E8" s="9" t="inlineStr">
+      <c r="E8" s="6" t="inlineStr">
         <is>
           <t>11/6 電路板下單</t>
         </is>
       </c>
-      <c r="F8" s="8" t="inlineStr">
+      <c r="F8" s="5" t="inlineStr">
         <is>
           <t>3,000 台加備品已下單，供應商確認 12/4 前到廠</t>
         </is>
       </c>
     </row>
     <row r="9" ht="40" customHeight="1">
-      <c r="A9" s="7" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>W5</t>
         </is>
       </c>
-      <c r="B9" s="7" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>11/9–11/13</t>
         </is>
       </c>
-      <c r="C9" s="8" t="inlineStr">
+      <c r="C9" s="5" t="inlineStr">
         <is>
           <t>外觀簽樣；訂面料和配件</t>
         </is>
       </c>
-      <c r="D9" s="8" t="inlineStr">
+      <c r="D9" s="5" t="inlineStr">
         <is>
           <t>客戶確認外觀；App 開發</t>
         </is>
       </c>
-      <c r="E9" s="9" t="inlineStr">
+      <c r="E9" s="6" t="inlineStr">
         <is>
           <t>11/13 外觀簽樣</t>
         </is>
       </c>
-      <c r="F9" s="8" t="inlineStr">
+      <c r="F9" s="5" t="inlineStr">
         <is>
           <t>款式 A 兩個造型、款式 B 由客戶書面簽樣；簽樣品雙方各留一隻</t>
         </is>
       </c>
     </row>
     <row r="10" ht="40" customHeight="1">
-      <c r="A10" s="7" t="inlineStr">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>W6</t>
         </is>
       </c>
-      <c r="B10" s="7" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>11/16–11/20</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="5" t="inlineStr">
         <is>
           <t>T1 試模；包裝打樣</t>
         </is>
       </c>
-      <c r="D10" s="8" t="inlineStr">
+      <c r="D10" s="5" t="inlineStr">
         <is>
           <t>成品送檢（玩具安全、無線、電池）；App 開發</t>
         </is>
       </c>
-      <c r="E10" s="9" t="inlineStr">
+      <c r="E10" s="6" t="inlineStr">
         <is>
           <t>11/20 款式 A 兩款數量</t>
         </is>
       </c>
-      <c r="F10" s="8" t="inlineStr">
+      <c r="F10" s="5" t="inlineStr">
         <is>
           <t>客戶書面確認兩個造型各多少</t>
         </is>
       </c>
     </row>
     <row r="11" ht="40" customHeight="1">
-      <c r="A11" s="7" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>W7</t>
         </is>
       </c>
-      <c r="B11" s="7" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>11/23–11/27</t>
         </is>
       </c>
-      <c r="C11" s="8" t="inlineStr">
+      <c r="C11" s="5" t="inlineStr">
         <is>
           <t>產前樣；包裝定稿</t>
         </is>
       </c>
-      <c r="D11" s="8" t="inlineStr">
+      <c r="D11" s="5" t="inlineStr">
         <is>
           <t>確認產前樣、下大貨單；出廠韌體交電路板供應商；App 測試版</t>
         </is>
       </c>
-      <c r="E11" s="9" t="inlineStr">
+      <c r="E11" s="6" t="inlineStr">
         <is>
           <t>11/27 產前樣、大貨單</t>
         </is>
       </c>
-      <c r="F11" s="8" t="inlineStr">
+      <c r="F11" s="5" t="inlineStr">
         <is>
           <t>產前樣雙方簽字；大貨單已發出；三個 App 測試版可以安裝使用</t>
         </is>
       </c>
     </row>
     <row r="12" ht="40" customHeight="1">
-      <c r="A12" s="7" t="inlineStr">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>W8</t>
         </is>
       </c>
-      <c r="B12" s="7" t="inlineStr">
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>11/30–12/4</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="5" t="inlineStr">
         <is>
           <t>物料和電路板到廠，排產線</t>
         </is>
       </c>
-      <c r="D12" s="8" t="inlineStr">
+      <c r="D12" s="5" t="inlineStr">
         <is>
           <t>交燒錄自檢工位和作業指導書；App 提交蘋果和 Google 審核</t>
         </is>
       </c>
-      <c r="E12" s="9" t="inlineStr">
+      <c r="E12" s="6" t="inlineStr">
         <is>
           <t>11/30 App 送審</t>
         </is>
       </c>
-      <c r="F12" s="8" t="inlineStr">
+      <c r="F12" s="5" t="inlineStr">
         <is>
           <t>三個 App 已提交審核</t>
         </is>
       </c>
     </row>
     <row r="13" ht="40" customHeight="1">
-      <c r="A13" s="7" t="inlineStr">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>W9</t>
         </is>
       </c>
-      <c r="B13" s="7" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>12/7–12/11</t>
         </is>
       </c>
-      <c r="C13" s="8" t="inlineStr">
+      <c r="C13" s="5" t="inlineStr">
         <is>
           <t>試產 50–100 隻</t>
         </is>
       </c>
-      <c r="D13" s="8" t="inlineStr">
+      <c r="D13" s="5" t="inlineStr">
         <is>
           <t>全檢試產品；App 審核（預留被拒重交的時間）</t>
         </is>
       </c>
-      <c r="E13" s="9" t="inlineStr">
+      <c r="E13" s="6" t="inlineStr">
         <is>
           <t>12/11 試產、App 過審</t>
         </is>
       </c>
-      <c r="F13" s="8" t="inlineStr">
+      <c r="F13" s="5" t="inlineStr">
         <is>
           <t>試產全檢合格，問題已改好；三個 App 通過審核；檢測報告合格</t>
         </is>
       </c>
     </row>
     <row r="14" ht="40" customHeight="1">
-      <c r="A14" s="7" t="inlineStr">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>W10</t>
         </is>
       </c>
-      <c r="B14" s="7" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>12/14–12/18</t>
         </is>
       </c>
-      <c r="C14" s="8" t="inlineStr">
+      <c r="C14" s="5" t="inlineStr">
         <is>
           <t>大貨開始，每日回報產量和不良率</t>
         </is>
       </c>
-      <c r="D14" s="8" t="inlineStr">
+      <c r="D14" s="5" t="inlineStr">
         <is>
           <t>App 上架但不公開，客戶驗收</t>
         </is>
       </c>
-      <c r="E14" s="9" t="inlineStr">
+      <c r="E14" s="6" t="inlineStr">
         <is>
           <t>12/14 大貨開始</t>
         </is>
       </c>
-      <c r="F14" s="8" t="inlineStr"/>
+      <c r="F14" s="5" t="inlineStr"/>
     </row>
     <row r="15" ht="24" customHeight="1">
-      <c r="A15" s="4" t="inlineStr">
+      <c r="A15" s="7" t="inlineStr">
         <is>
           <t>W11</t>
         </is>
       </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B15" s="7" t="inlineStr">
         <is>
           <t>12/21–12/25</t>
         </is>
       </c>
-      <c r="C15" s="5" t="inlineStr">
+      <c r="C15" s="8" t="inlineStr">
         <is>
           <t>大貨生產；中期驗貨</t>
         </is>
       </c>
-      <c r="D15" s="5" t="inlineStr">
+      <c r="D15" s="8" t="inlineStr">
         <is>
           <t>12/25–26 香港假期</t>
         </is>
       </c>
-      <c r="E15" s="6" t="inlineStr"/>
-      <c r="F15" s="5" t="inlineStr"/>
+      <c r="E15" s="9" t="inlineStr"/>
+      <c r="F15" s="8" t="inlineStr"/>
     </row>
     <row r="16" ht="24" customHeight="1">
-      <c r="A16" s="7" t="inlineStr">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>W12</t>
         </is>
       </c>
-      <c r="B16" s="7" t="inlineStr">
+      <c r="B16" s="4" t="inlineStr">
         <is>
           <t>12/28–1/1</t>
         </is>
       </c>
-      <c r="C16" s="8" t="inlineStr">
+      <c r="C16" s="5" t="inlineStr">
         <is>
           <t>大貨完成</t>
         </is>
       </c>
-      <c r="D16" s="8" t="inlineStr">
+      <c r="D16" s="5" t="inlineStr">
         <is>
           <t>1/1 假期</t>
         </is>
       </c>
-      <c r="E16" s="9" t="inlineStr">
+      <c r="E16" s="6" t="inlineStr">
         <is>
           <t>12/31 大貨完成</t>
         </is>
       </c>
-      <c r="F16" s="8" t="inlineStr">
+      <c r="F16" s="5" t="inlineStr">
         <is>
           <t>全部數量完成；中期驗貨合格</t>
         </is>
       </c>
     </row>
     <row r="17" ht="40" customHeight="1">
-      <c r="A17" s="4" t="inlineStr">
+      <c r="A17" s="7" t="inlineStr">
         <is>
           <t>W13</t>
         </is>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B17" s="7" t="inlineStr">
         <is>
           <t>1/4–1/8</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr">
+      <c r="C17" s="8" t="inlineStr">
         <is>
           <t>緩衝週：返工、補貨；尾期驗貨</t>
         </is>
       </c>
-      <c r="D17" s="5" t="inlineStr">
+      <c r="D17" s="8" t="inlineStr">
         <is>
           <t>客戶確認 App 公開日期</t>
         </is>
       </c>
-      <c r="E17" s="6" t="inlineStr"/>
-      <c r="F17" s="5" t="inlineStr"/>
+      <c r="E17" s="9" t="inlineStr"/>
+      <c r="F17" s="8" t="inlineStr"/>
     </row>
     <row r="18" ht="40" customHeight="1">
-      <c r="A18" s="7" t="inlineStr">
+      <c r="A18" s="4" t="inlineStr">
         <is>
           <t>W14</t>
         </is>
       </c>
-      <c r="B18" s="7" t="inlineStr">
+      <c r="B18" s="4" t="inlineStr">
         <is>
           <t>1/11–1/15</t>
         </is>
       </c>
-      <c r="C18" s="8" t="inlineStr">
+      <c r="C18" s="5" t="inlineStr">
         <is>
           <t>包裝、裝箱、出貨</t>
         </is>
       </c>
-      <c r="D18" s="8" t="inlineStr">
+      <c r="D18" s="5" t="inlineStr">
         <is>
           <t>App 公開上架</t>
         </is>
       </c>
-      <c r="E18" s="9" t="inlineStr">
+      <c r="E18" s="6" t="inlineStr">
         <is>
           <t>1/15 出貨</t>
         </is>
       </c>
-      <c r="F18" s="8" t="inlineStr">
+      <c r="F18" s="5" t="inlineStr">
         <is>
           <t>尾期驗貨合格；出貨清單和序號／MAC 對照表；每台已在系統登記</t>
         </is>
       </c>
     </row>
     <row r="19" ht="24" customHeight="1">
-      <c r="A19" s="7" t="inlineStr">
+      <c r="A19" s="4" t="inlineStr">
         <is>
           <t>W15–16</t>
         </is>
       </c>
-      <c r="B19" s="7" t="inlineStr">
+      <c r="B19" s="4" t="inlineStr">
         <is>
           <t>1/18–1/29</t>
         </is>
       </c>
-      <c r="C19" s="8" t="inlineStr"/>
-      <c r="D19" s="8" t="inlineStr">
+      <c r="C19" s="5" t="inlineStr"/>
+      <c r="D19" s="5" t="inlineStr">
         <is>
           <t>運送、簽收</t>
         </is>
       </c>
-      <c r="E19" s="9" t="inlineStr">
+      <c r="E19" s="6" t="inlineStr">
         <is>
           <t>1/29 送達</t>
         </is>
       </c>
-      <c r="F19" s="8" t="inlineStr">
+      <c r="F19" s="5" t="inlineStr">
         <is>
           <t>全部簽收</t>
         </is>
@@ -1070,157 +1078,157 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="9" t="inlineStr">
         <is>
           <t>收音</t>
         </is>
       </c>
-      <c r="B2" s="5" t="inlineStr">
+      <c r="B2" s="8" t="inlineStr">
         <is>
           <t>距離 1 米正常說話，語音識別正確；和裸板比較不能明顯變差</t>
         </is>
       </c>
-      <c r="C2" s="4" t="inlineStr"/>
-      <c r="D2" s="4" t="inlineStr"/>
-      <c r="E2" s="4" t="inlineStr"/>
-      <c r="F2" s="4" t="inlineStr"/>
-      <c r="G2" s="4" t="inlineStr"/>
+      <c r="C2" s="7" t="inlineStr"/>
+      <c r="D2" s="7" t="inlineStr"/>
+      <c r="E2" s="7" t="inlineStr"/>
+      <c r="F2" s="7" t="inlineStr"/>
+      <c r="G2" s="7" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="inlineStr">
+      <c r="A3" s="9" t="inlineStr">
         <is>
           <t>喇叭</t>
         </is>
       </c>
-      <c r="B3" s="5" t="inlineStr">
+      <c r="B3" s="8" t="inlineStr">
         <is>
           <t>隔著布料的響度和清晰度；最大音量不破音、不震動</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr"/>
-      <c r="D3" s="4" t="inlineStr"/>
-      <c r="E3" s="4" t="inlineStr"/>
-      <c r="F3" s="4" t="inlineStr"/>
-      <c r="G3" s="4" t="inlineStr"/>
+      <c r="C3" s="7" t="inlineStr"/>
+      <c r="D3" s="7" t="inlineStr"/>
+      <c r="E3" s="7" t="inlineStr"/>
+      <c r="F3" s="7" t="inlineStr"/>
+      <c r="G3" s="7" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="9" t="inlineStr">
         <is>
           <t>按鍵</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="8" t="inlineStr">
         <is>
           <t>隔著布料／徽章按得到，小朋友按得動，回彈清楚</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr"/>
-      <c r="D4" s="4" t="inlineStr"/>
-      <c r="E4" s="4" t="inlineStr"/>
-      <c r="F4" s="4" t="inlineStr"/>
-      <c r="G4" s="4" t="inlineStr"/>
+      <c r="C4" s="7" t="inlineStr"/>
+      <c r="D4" s="7" t="inlineStr"/>
+      <c r="E4" s="7" t="inlineStr"/>
+      <c r="F4" s="7" t="inlineStr"/>
+      <c r="G4" s="7" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="A5" s="9" t="inlineStr">
         <is>
           <t>Wi-Fi</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="8" t="inlineStr">
         <is>
           <t>裝進公仔後訊號強度，和裸板比較</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr"/>
-      <c r="D5" s="4" t="inlineStr"/>
-      <c r="E5" s="4" t="inlineStr"/>
-      <c r="F5" s="4" t="inlineStr"/>
-      <c r="G5" s="4" t="inlineStr"/>
+      <c r="C5" s="7" t="inlineStr"/>
+      <c r="D5" s="7" t="inlineStr"/>
+      <c r="E5" s="7" t="inlineStr"/>
+      <c r="F5" s="7" t="inlineStr"/>
+      <c r="G5" s="7" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="9" t="inlineStr">
         <is>
           <t>充電</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B6" s="8" t="inlineStr">
         <is>
           <t>USB-C 插得進，充電時燈號看得到</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr"/>
-      <c r="D6" s="4" t="inlineStr"/>
-      <c r="E6" s="4" t="inlineStr"/>
-      <c r="F6" s="4" t="inlineStr"/>
-      <c r="G6" s="4" t="inlineStr"/>
+      <c r="C6" s="7" t="inlineStr"/>
+      <c r="D6" s="7" t="inlineStr"/>
+      <c r="E6" s="7" t="inlineStr"/>
+      <c r="F6" s="7" t="inlineStr"/>
+      <c r="G6" s="7" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="A7" s="9" t="inlineStr">
         <is>
           <t>燈號</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B7" s="8" t="inlineStr">
         <is>
           <t>低電紅燈從外面看得到（或確定不外露）</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr"/>
-      <c r="D7" s="4" t="inlineStr"/>
-      <c r="E7" s="4" t="inlineStr"/>
-      <c r="F7" s="4" t="inlineStr"/>
-      <c r="G7" s="4" t="inlineStr"/>
+      <c r="C7" s="7" t="inlineStr"/>
+      <c r="D7" s="7" t="inlineStr"/>
+      <c r="E7" s="7" t="inlineStr"/>
+      <c r="F7" s="7" t="inlineStr"/>
+      <c r="G7" s="7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" s="9" t="inlineStr">
         <is>
           <t>跌落</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B8" s="8" t="inlineStr">
         <is>
           <t>1 米跌落，零件不脫落，機芯盒不鬆脫</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr"/>
-      <c r="D8" s="4" t="inlineStr"/>
-      <c r="E8" s="4" t="inlineStr"/>
-      <c r="F8" s="4" t="inlineStr"/>
-      <c r="G8" s="4" t="inlineStr"/>
+      <c r="C8" s="7" t="inlineStr"/>
+      <c r="D8" s="7" t="inlineStr"/>
+      <c r="E8" s="7" t="inlineStr"/>
+      <c r="F8" s="7" t="inlineStr"/>
+      <c r="G8" s="7" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="6" t="inlineStr">
+      <c r="A9" s="9" t="inlineStr">
         <is>
           <t>小零件與尖角</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B9" s="8" t="inlineStr">
         <is>
           <t>眼睛、徽章、配件拉力測試；沒有尖角和可吞食的小零件</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr"/>
-      <c r="D9" s="4" t="inlineStr"/>
-      <c r="E9" s="4" t="inlineStr"/>
-      <c r="F9" s="4" t="inlineStr"/>
-      <c r="G9" s="4" t="inlineStr"/>
+      <c r="C9" s="7" t="inlineStr"/>
+      <c r="D9" s="7" t="inlineStr"/>
+      <c r="E9" s="7" t="inlineStr"/>
+      <c r="F9" s="7" t="inlineStr"/>
+      <c r="G9" s="7" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="A10" s="9" t="inlineStr">
         <is>
           <t>拆裝</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B10" s="8" t="inlineStr">
         <is>
           <t>機芯盒能取出維修，縫口或拉鍊位置合理</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr"/>
-      <c r="D10" s="4" t="inlineStr"/>
-      <c r="E10" s="4" t="inlineStr"/>
-      <c r="F10" s="4" t="inlineStr"/>
-      <c r="G10" s="4" t="inlineStr"/>
+      <c r="C10" s="7" t="inlineStr"/>
+      <c r="D10" s="7" t="inlineStr"/>
+      <c r="E10" s="7" t="inlineStr"/>
+      <c r="F10" s="7" t="inlineStr"/>
+      <c r="G10" s="7" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">

--- a/docs/毛公仔打版與量產時間表_草案v0.5.xlsx
+++ b/docs/毛公仔打版與量產時間表_草案v0.5.xlsx
@@ -8,7 +8,8 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="時間表" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="樣品測試項目" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="App 開發與上架" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="樣品測試項目" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'時間表'!$4:$4</definedName>
@@ -20,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -55,6 +56,12 @@
       <b val="1"/>
       <color rgb="0017202B"/>
       <sz val="10.5"/>
+    </font>
+    <font>
+      <name val="Microsoft JhengHei"/>
+      <b val="1"/>
+      <color rgb="0017202B"/>
+      <sz val="14"/>
     </font>
   </fonts>
   <fills count="4">
@@ -101,7 +108,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -126,6 +133,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -856,7 +864,7 @@
       </c>
       <c r="F14" s="5" t="inlineStr"/>
     </row>
-    <row r="15" ht="24" customHeight="1">
+    <row r="15" ht="40" customHeight="1">
       <c r="A15" s="7" t="inlineStr">
         <is>
           <t>W11</t>
@@ -968,7 +976,7 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="24" customHeight="1">
+    <row r="19" ht="40" customHeight="1">
       <c r="A19" s="4" t="inlineStr">
         <is>
           <t>W15–16</t>
@@ -1023,6 +1031,281 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:D13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="70" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="10" t="inlineStr">
+        <is>
+          <t>App 開發與上架：里程碑和驗收標準</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>網頁 App 包在原生殼裡，三個品牌各一個 App。殼過審後，網頁畫面可以繼續更新，不用重新送審。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>週次</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>日期</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>里程碑</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>驗收標準（全部做到才算完成）</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="72" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>W2</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>10/23</t>
+        </is>
+      </c>
+      <c r="C5" s="9" t="inlineStr">
+        <is>
+          <t>對接方案定案</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>① 網頁和殼的對接清單：藍牙配網、原生登入、推送、麥克風、刪除帳號、深層連結，每項寫明介面、參數、回傳和錯誤
+② 做殼的同事書面確認
+③ 三個 App 的名稱、圖示、bundle id 定好</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="72" customHeight="1">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>W3</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>10/30</t>
+        </is>
+      </c>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>登入和品牌主題</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>① email 驗證碼登入可用；Google／Apple 登入由殼完成，網頁收得到登入結果
+② App 內可以刪除帳號
+③ 三個品牌各自的顏色、logo、文案顯示正確，畫面不閃</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="72" customHeight="1">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>W4</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>11/6</t>
+        </is>
+      </c>
+      <c r="C7" s="9" t="inlineStr">
+        <is>
+          <t>AI Buddy App 可以內部測試</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>① iPhone 和 Android 都能用藍牙找到玩具、選 Wi-Fi、完成綁定，10 分鐘內做完
+② 選角色、對話、改設定、解綁都正常
+③ 家長控制（家長鎖、每日上限）可用</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="56" customHeight="1">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>W6</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>11/20</t>
+        </is>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>快活和政協青年聯會 App 頁面完成</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>① 快活：會員綁定、查看記憶、一鍵忘記、選語言（粵／普／英）
+② 政協青年聯會版：品牌頁面和角色
+③ 三個 App 都有測試版可以安裝（TestFlight、Google 內部測試）</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="88" customHeight="1">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>W7</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>11/27</t>
+        </is>
+      </c>
+      <c r="C9" s="9" t="inlineStr">
+        <is>
+          <t>功能凍結</t>
+        </is>
+      </c>
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>① 三個 App 全流程通過：安裝 → 登入 → 藍牙配網 → 綁定 → 對話 → 解綁；iOS 和 Android 各至少兩款手機
+② Wi-Fi 密碼錯、玩具已被別人綁定、斷網時都有清楚提示
+③ 推送收得到：玩具第一次上線、低電提醒
+④ 連續使用 30 分鐘不閃退</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="56" customHeight="1">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>W8</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>11/30</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>提交商店審核</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>① 上架資料齊全：截圖、描述、私隱政策網址、私隱標籤、審核用測試帳號、玩具示範影片
+② 三個 App 已提交蘋果和 Google</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="40" customHeight="1">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>W9</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>12/11</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="inlineStr">
+        <is>
+          <t>通過審核</t>
+        </is>
+      </c>
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t>① 三個 App 都通過蘋果和 Google 審核
+② 如果被拒，修改後重交並通過</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="56" customHeight="1">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>W10</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>12/18</t>
+        </is>
+      </c>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>客戶驗收</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>① 馬會、政協青年聯會用正式版走一次完整流程，書面確認
+② 找 3 位非團隊成員，從開箱到第一次對話都在 10 分鐘內完成
+③ App 已上架但不公開</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="40" customHeight="1">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>W14</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>1/15</t>
+        </is>
+      </c>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>公開上架</t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="inlineStr">
+        <is>
+          <t>① 三個 App 公開，用戶搜尋得到
+② App 內看得到客服聯絡方式、常見問題、保修條款</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/docs/毛公仔打版與量產時間表_草案v0.5.xlsx
+++ b/docs/毛公仔打版與量產時間表_草案v0.5.xlsx
@@ -108,26 +108,23 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -582,35 +579,35 @@
           <t>10/16 全部造型交工廠</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="F5" s="7" t="inlineStr">
         <is>
           <t>馬會兩款、政協青年聯會版、AI Buddy（如 1/15 出貨）的造型圖（正、側、背面，尺寸，顏色）全部交到工廠；工廠回覆打樣排期</t>
         </is>
       </c>
     </row>
     <row r="6" ht="40" customHeight="1">
-      <c r="A6" s="7" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>W2</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>10/19–10/23</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="5" t="inlineStr">
         <is>
           <t>機芯盒 3D 設計、第一版初樣</t>
         </is>
       </c>
-      <c r="D6" s="8" t="inlineStr">
+      <c r="D6" s="5" t="inlineStr">
         <is>
           <t>審 3D 圖；決定電路板改不改；定好 App 和網頁的對接方式</t>
         </is>
       </c>
-      <c r="E6" s="9" t="inlineStr"/>
-      <c r="F6" s="8" t="inlineStr"/>
+      <c r="E6" s="8" t="inlineStr"/>
+      <c r="F6" s="5" t="inlineStr"/>
     </row>
     <row r="7" ht="56" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
@@ -638,7 +635,7 @@
           <t>10/30 第一版樣品測試</t>
         </is>
       </c>
-      <c r="F7" s="5" t="inlineStr">
+      <c r="F7" s="7" t="inlineStr">
         <is>
           <t>收音（1 米）、喇叭響度、按鍵、Wi-Fi、充電、跌落全部測過；修改意見已交工廠</t>
         </is>
@@ -670,7 +667,7 @@
           <t>11/6 電路板下單</t>
         </is>
       </c>
-      <c r="F8" s="5" t="inlineStr">
+      <c r="F8" s="7" t="inlineStr">
         <is>
           <t>3,000 台加備品已下單，供應商確認 12/4 前到廠</t>
         </is>
@@ -702,7 +699,7 @@
           <t>11/13 外觀簽樣</t>
         </is>
       </c>
-      <c r="F9" s="5" t="inlineStr">
+      <c r="F9" s="7" t="inlineStr">
         <is>
           <t>款式 A 兩個造型、款式 B 由客戶書面簽樣；簽樣品雙方各留一隻</t>
         </is>
@@ -734,7 +731,7 @@
           <t>11/20 款式 A 兩款數量</t>
         </is>
       </c>
-      <c r="F10" s="5" t="inlineStr">
+      <c r="F10" s="7" t="inlineStr">
         <is>
           <t>客戶書面確認兩個造型各多少</t>
         </is>
@@ -766,7 +763,7 @@
           <t>11/27 產前樣、大貨單</t>
         </is>
       </c>
-      <c r="F11" s="5" t="inlineStr">
+      <c r="F11" s="7" t="inlineStr">
         <is>
           <t>產前樣雙方簽字；大貨單已發出；三個 App 測試版可以安裝使用</t>
         </is>
@@ -798,7 +795,7 @@
           <t>11/30 App 送審</t>
         </is>
       </c>
-      <c r="F12" s="5" t="inlineStr">
+      <c r="F12" s="7" t="inlineStr">
         <is>
           <t>三個 App 已提交審核</t>
         </is>
@@ -830,7 +827,7 @@
           <t>12/11 試產、App 過審</t>
         </is>
       </c>
-      <c r="F13" s="5" t="inlineStr">
+      <c r="F13" s="7" t="inlineStr">
         <is>
           <t>試產全檢合格，問題已改好；三個 App 通過審核；檢測報告合格</t>
         </is>
@@ -862,31 +859,31 @@
           <t>12/14 大貨開始</t>
         </is>
       </c>
-      <c r="F14" s="5" t="inlineStr"/>
+      <c r="F14" s="7" t="inlineStr"/>
     </row>
     <row r="15" ht="40" customHeight="1">
-      <c r="A15" s="7" t="inlineStr">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>W11</t>
         </is>
       </c>
-      <c r="B15" s="7" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>12/21–12/25</t>
         </is>
       </c>
-      <c r="C15" s="8" t="inlineStr">
+      <c r="C15" s="5" t="inlineStr">
         <is>
           <t>大貨生產；中期驗貨</t>
         </is>
       </c>
-      <c r="D15" s="8" t="inlineStr">
+      <c r="D15" s="5" t="inlineStr">
         <is>
           <t>12/25–26 香港假期</t>
         </is>
       </c>
-      <c r="E15" s="9" t="inlineStr"/>
-      <c r="F15" s="8" t="inlineStr"/>
+      <c r="E15" s="8" t="inlineStr"/>
+      <c r="F15" s="5" t="inlineStr"/>
     </row>
     <row r="16" ht="24" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
@@ -914,35 +911,35 @@
           <t>12/31 大貨完成</t>
         </is>
       </c>
-      <c r="F16" s="5" t="inlineStr">
+      <c r="F16" s="7" t="inlineStr">
         <is>
           <t>全部數量完成；中期驗貨合格</t>
         </is>
       </c>
     </row>
     <row r="17" ht="40" customHeight="1">
-      <c r="A17" s="7" t="inlineStr">
+      <c r="A17" s="4" t="inlineStr">
         <is>
           <t>W13</t>
         </is>
       </c>
-      <c r="B17" s="7" t="inlineStr">
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>1/4–1/8</t>
         </is>
       </c>
-      <c r="C17" s="8" t="inlineStr">
+      <c r="C17" s="5" t="inlineStr">
         <is>
           <t>緩衝週：返工、補貨；尾期驗貨</t>
         </is>
       </c>
-      <c r="D17" s="8" t="inlineStr">
+      <c r="D17" s="5" t="inlineStr">
         <is>
           <t>客戶確認 App 公開日期</t>
         </is>
       </c>
-      <c r="E17" s="9" t="inlineStr"/>
-      <c r="F17" s="8" t="inlineStr"/>
+      <c r="E17" s="8" t="inlineStr"/>
+      <c r="F17" s="5" t="inlineStr"/>
     </row>
     <row r="18" ht="40" customHeight="1">
       <c r="A18" s="4" t="inlineStr">
@@ -970,7 +967,7 @@
           <t>1/15 出貨</t>
         </is>
       </c>
-      <c r="F18" s="5" t="inlineStr">
+      <c r="F18" s="7" t="inlineStr">
         <is>
           <t>尾期驗貨合格；出貨清單和序號／MAC 對照表；每台已在系統登記</t>
         </is>
@@ -998,7 +995,7 @@
           <t>1/29 送達</t>
         </is>
       </c>
-      <c r="F19" s="5" t="inlineStr">
+      <c r="F19" s="7" t="inlineStr">
         <is>
           <t>全部簽收</t>
         </is>
@@ -1007,7 +1004,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>黃色行是關鍵節點：延誤的話，後面的日期會跟著推遲，請提早通知。</t>
+          <t>黃色格是關鍵節點和驗收標準：延誤的話，後面的日期會跟著推遲，請提早通知。</t>
         </is>
       </c>
     </row>
@@ -1046,7 +1043,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="10" t="inlineStr">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>App 開發與上架：里程碑和驗收標準</t>
         </is>
@@ -1082,22 +1079,22 @@
       </c>
     </row>
     <row r="5" ht="72" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>W2</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>10/23</t>
         </is>
       </c>
-      <c r="C5" s="9" t="inlineStr">
+      <c r="C5" s="8" t="inlineStr">
         <is>
           <t>對接方案定案</t>
         </is>
       </c>
-      <c r="D5" s="8" t="inlineStr">
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>① 網頁和殼的對接清單：藍牙配網、原生登入、推送、麥克風、刪除帳號、深層連結，每項寫明介面、參數、回傳和錯誤
 ② 做殼的同事書面確認
@@ -1106,22 +1103,22 @@
       </c>
     </row>
     <row r="6" ht="72" customHeight="1">
-      <c r="A6" s="7" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>W3</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>10/30</t>
         </is>
       </c>
-      <c r="C6" s="9" t="inlineStr">
+      <c r="C6" s="8" t="inlineStr">
         <is>
           <t>登入和品牌主題</t>
         </is>
       </c>
-      <c r="D6" s="8" t="inlineStr">
+      <c r="D6" s="5" t="inlineStr">
         <is>
           <t>① email 驗證碼登入可用；Google／Apple 登入由殼完成，網頁收得到登入結果
 ② App 內可以刪除帳號
@@ -1130,22 +1127,22 @@
       </c>
     </row>
     <row r="7" ht="72" customHeight="1">
-      <c r="A7" s="7" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>W4</t>
         </is>
       </c>
-      <c r="B7" s="7" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>11/6</t>
         </is>
       </c>
-      <c r="C7" s="9" t="inlineStr">
+      <c r="C7" s="8" t="inlineStr">
         <is>
           <t>AI Buddy App 可以內部測試</t>
         </is>
       </c>
-      <c r="D7" s="8" t="inlineStr">
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>① iPhone 和 Android 都能用藍牙找到玩具、選 Wi-Fi、完成綁定，10 分鐘內做完
 ② 選角色、對話、改設定、解綁都正常
@@ -1154,22 +1151,22 @@
       </c>
     </row>
     <row r="8" ht="56" customHeight="1">
-      <c r="A8" s="7" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>W6</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>11/20</t>
         </is>
       </c>
-      <c r="C8" s="9" t="inlineStr">
+      <c r="C8" s="8" t="inlineStr">
         <is>
           <t>快活和政協青年聯會 App 頁面完成</t>
         </is>
       </c>
-      <c r="D8" s="8" t="inlineStr">
+      <c r="D8" s="5" t="inlineStr">
         <is>
           <t>① 快活：會員綁定、查看記憶、一鍵忘記、選語言（粵／普／英）
 ② 政協青年聯會版：品牌頁面和角色
@@ -1178,22 +1175,22 @@
       </c>
     </row>
     <row r="9" ht="88" customHeight="1">
-      <c r="A9" s="7" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>W7</t>
         </is>
       </c>
-      <c r="B9" s="7" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>11/27</t>
         </is>
       </c>
-      <c r="C9" s="9" t="inlineStr">
+      <c r="C9" s="8" t="inlineStr">
         <is>
           <t>功能凍結</t>
         </is>
       </c>
-      <c r="D9" s="8" t="inlineStr">
+      <c r="D9" s="5" t="inlineStr">
         <is>
           <t>① 三個 App 全流程通過：安裝 → 登入 → 藍牙配網 → 綁定 → 對話 → 解綁；iOS 和 Android 各至少兩款手機
 ② Wi-Fi 密碼錯、玩具已被別人綁定、斷網時都有清楚提示
@@ -1203,22 +1200,22 @@
       </c>
     </row>
     <row r="10" ht="56" customHeight="1">
-      <c r="A10" s="7" t="inlineStr">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>W8</t>
         </is>
       </c>
-      <c r="B10" s="7" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>11/30</t>
         </is>
       </c>
-      <c r="C10" s="9" t="inlineStr">
+      <c r="C10" s="8" t="inlineStr">
         <is>
           <t>提交商店審核</t>
         </is>
       </c>
-      <c r="D10" s="8" t="inlineStr">
+      <c r="D10" s="5" t="inlineStr">
         <is>
           <t>① 上架資料齊全：截圖、描述、私隱政策網址、私隱標籤、審核用測試帳號、玩具示範影片
 ② 三個 App 已提交蘋果和 Google</t>
@@ -1226,22 +1223,22 @@
       </c>
     </row>
     <row r="11" ht="40" customHeight="1">
-      <c r="A11" s="7" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>W9</t>
         </is>
       </c>
-      <c r="B11" s="7" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>12/11</t>
         </is>
       </c>
-      <c r="C11" s="9" t="inlineStr">
+      <c r="C11" s="8" t="inlineStr">
         <is>
           <t>通過審核</t>
         </is>
       </c>
-      <c r="D11" s="8" t="inlineStr">
+      <c r="D11" s="5" t="inlineStr">
         <is>
           <t>① 三個 App 都通過蘋果和 Google 審核
 ② 如果被拒，修改後重交並通過</t>
@@ -1249,22 +1246,22 @@
       </c>
     </row>
     <row r="12" ht="56" customHeight="1">
-      <c r="A12" s="7" t="inlineStr">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>W10</t>
         </is>
       </c>
-      <c r="B12" s="7" t="inlineStr">
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>12/18</t>
         </is>
       </c>
-      <c r="C12" s="9" t="inlineStr">
+      <c r="C12" s="8" t="inlineStr">
         <is>
           <t>客戶驗收</t>
         </is>
       </c>
-      <c r="D12" s="8" t="inlineStr">
+      <c r="D12" s="5" t="inlineStr">
         <is>
           <t>① 馬會、政協青年聯會用正式版走一次完整流程，書面確認
 ② 找 3 位非團隊成員，從開箱到第一次對話都在 10 分鐘內完成
@@ -1273,22 +1270,22 @@
       </c>
     </row>
     <row r="13" ht="40" customHeight="1">
-      <c r="A13" s="7" t="inlineStr">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>W14</t>
         </is>
       </c>
-      <c r="B13" s="7" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>1/15</t>
         </is>
       </c>
-      <c r="C13" s="9" t="inlineStr">
+      <c r="C13" s="8" t="inlineStr">
         <is>
           <t>公開上架</t>
         </is>
       </c>
-      <c r="D13" s="8" t="inlineStr">
+      <c r="D13" s="5" t="inlineStr">
         <is>
           <t>① 三個 App 公開，用戶搜尋得到
 ② App 內看得到客服聯絡方式、常見問題、保修條款</t>
@@ -1361,157 +1358,157 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="9" t="inlineStr">
+      <c r="A2" s="8" t="inlineStr">
         <is>
           <t>收音</t>
         </is>
       </c>
-      <c r="B2" s="8" t="inlineStr">
+      <c r="B2" s="5" t="inlineStr">
         <is>
           <t>距離 1 米正常說話，語音識別正確；和裸板比較不能明顯變差</t>
         </is>
       </c>
-      <c r="C2" s="7" t="inlineStr"/>
-      <c r="D2" s="7" t="inlineStr"/>
-      <c r="E2" s="7" t="inlineStr"/>
-      <c r="F2" s="7" t="inlineStr"/>
-      <c r="G2" s="7" t="inlineStr"/>
+      <c r="C2" s="4" t="inlineStr"/>
+      <c r="D2" s="4" t="inlineStr"/>
+      <c r="E2" s="4" t="inlineStr"/>
+      <c r="F2" s="4" t="inlineStr"/>
+      <c r="G2" s="4" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="9" t="inlineStr">
+      <c r="A3" s="8" t="inlineStr">
         <is>
           <t>喇叭</t>
         </is>
       </c>
-      <c r="B3" s="8" t="inlineStr">
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t>隔著布料的響度和清晰度；最大音量不破音、不震動</t>
         </is>
       </c>
-      <c r="C3" s="7" t="inlineStr"/>
-      <c r="D3" s="7" t="inlineStr"/>
-      <c r="E3" s="7" t="inlineStr"/>
-      <c r="F3" s="7" t="inlineStr"/>
-      <c r="G3" s="7" t="inlineStr"/>
+      <c r="C3" s="4" t="inlineStr"/>
+      <c r="D3" s="4" t="inlineStr"/>
+      <c r="E3" s="4" t="inlineStr"/>
+      <c r="F3" s="4" t="inlineStr"/>
+      <c r="G3" s="4" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="9" t="inlineStr">
+      <c r="A4" s="8" t="inlineStr">
         <is>
           <t>按鍵</t>
         </is>
       </c>
-      <c r="B4" s="8" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>隔著布料／徽章按得到，小朋友按得動，回彈清楚</t>
         </is>
       </c>
-      <c r="C4" s="7" t="inlineStr"/>
-      <c r="D4" s="7" t="inlineStr"/>
-      <c r="E4" s="7" t="inlineStr"/>
-      <c r="F4" s="7" t="inlineStr"/>
-      <c r="G4" s="7" t="inlineStr"/>
+      <c r="C4" s="4" t="inlineStr"/>
+      <c r="D4" s="4" t="inlineStr"/>
+      <c r="E4" s="4" t="inlineStr"/>
+      <c r="F4" s="4" t="inlineStr"/>
+      <c r="G4" s="4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="9" t="inlineStr">
+      <c r="A5" s="8" t="inlineStr">
         <is>
           <t>Wi-Fi</t>
         </is>
       </c>
-      <c r="B5" s="8" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>裝進公仔後訊號強度，和裸板比較</t>
         </is>
       </c>
-      <c r="C5" s="7" t="inlineStr"/>
-      <c r="D5" s="7" t="inlineStr"/>
-      <c r="E5" s="7" t="inlineStr"/>
-      <c r="F5" s="7" t="inlineStr"/>
-      <c r="G5" s="7" t="inlineStr"/>
+      <c r="C5" s="4" t="inlineStr"/>
+      <c r="D5" s="4" t="inlineStr"/>
+      <c r="E5" s="4" t="inlineStr"/>
+      <c r="F5" s="4" t="inlineStr"/>
+      <c r="G5" s="4" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="inlineStr">
+      <c r="A6" s="8" t="inlineStr">
         <is>
           <t>充電</t>
         </is>
       </c>
-      <c r="B6" s="8" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>USB-C 插得進，充電時燈號看得到</t>
         </is>
       </c>
-      <c r="C6" s="7" t="inlineStr"/>
-      <c r="D6" s="7" t="inlineStr"/>
-      <c r="E6" s="7" t="inlineStr"/>
-      <c r="F6" s="7" t="inlineStr"/>
-      <c r="G6" s="7" t="inlineStr"/>
+      <c r="C6" s="4" t="inlineStr"/>
+      <c r="D6" s="4" t="inlineStr"/>
+      <c r="E6" s="4" t="inlineStr"/>
+      <c r="F6" s="4" t="inlineStr"/>
+      <c r="G6" s="4" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="9" t="inlineStr">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>燈號</t>
         </is>
       </c>
-      <c r="B7" s="8" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>低電紅燈從外面看得到（或確定不外露）</t>
         </is>
       </c>
-      <c r="C7" s="7" t="inlineStr"/>
-      <c r="D7" s="7" t="inlineStr"/>
-      <c r="E7" s="7" t="inlineStr"/>
-      <c r="F7" s="7" t="inlineStr"/>
-      <c r="G7" s="7" t="inlineStr"/>
+      <c r="C7" s="4" t="inlineStr"/>
+      <c r="D7" s="4" t="inlineStr"/>
+      <c r="E7" s="4" t="inlineStr"/>
+      <c r="F7" s="4" t="inlineStr"/>
+      <c r="G7" s="4" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="inlineStr">
+      <c r="A8" s="8" t="inlineStr">
         <is>
           <t>跌落</t>
         </is>
       </c>
-      <c r="B8" s="8" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>1 米跌落，零件不脫落，機芯盒不鬆脫</t>
         </is>
       </c>
-      <c r="C8" s="7" t="inlineStr"/>
-      <c r="D8" s="7" t="inlineStr"/>
-      <c r="E8" s="7" t="inlineStr"/>
-      <c r="F8" s="7" t="inlineStr"/>
-      <c r="G8" s="7" t="inlineStr"/>
+      <c r="C8" s="4" t="inlineStr"/>
+      <c r="D8" s="4" t="inlineStr"/>
+      <c r="E8" s="4" t="inlineStr"/>
+      <c r="F8" s="4" t="inlineStr"/>
+      <c r="G8" s="4" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="inlineStr">
+      <c r="A9" s="8" t="inlineStr">
         <is>
           <t>小零件與尖角</t>
         </is>
       </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B9" s="5" t="inlineStr">
         <is>
           <t>眼睛、徽章、配件拉力測試；沒有尖角和可吞食的小零件</t>
         </is>
       </c>
-      <c r="C9" s="7" t="inlineStr"/>
-      <c r="D9" s="7" t="inlineStr"/>
-      <c r="E9" s="7" t="inlineStr"/>
-      <c r="F9" s="7" t="inlineStr"/>
-      <c r="G9" s="7" t="inlineStr"/>
+      <c r="C9" s="4" t="inlineStr"/>
+      <c r="D9" s="4" t="inlineStr"/>
+      <c r="E9" s="4" t="inlineStr"/>
+      <c r="F9" s="4" t="inlineStr"/>
+      <c r="G9" s="4" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="9" t="inlineStr">
+      <c r="A10" s="8" t="inlineStr">
         <is>
           <t>拆裝</t>
         </is>
       </c>
-      <c r="B10" s="8" t="inlineStr">
+      <c r="B10" s="5" t="inlineStr">
         <is>
           <t>機芯盒能取出維修，縫口或拉鍊位置合理</t>
         </is>
       </c>
-      <c r="C10" s="7" t="inlineStr"/>
-      <c r="D10" s="7" t="inlineStr"/>
-      <c r="E10" s="7" t="inlineStr"/>
-      <c r="F10" s="7" t="inlineStr"/>
-      <c r="G10" s="7" t="inlineStr"/>
+      <c r="C10" s="4" t="inlineStr"/>
+      <c r="D10" s="4" t="inlineStr"/>
+      <c r="E10" s="4" t="inlineStr"/>
+      <c r="F10" s="4" t="inlineStr"/>
+      <c r="G10" s="4" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">

--- a/docs/毛公仔打版與量產時間表_草案v0.5.xlsx
+++ b/docs/毛公仔打版與量產時間表_草案v0.5.xlsx
@@ -118,10 +118,10 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -496,15 +496,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="36" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="36" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -534,26 +535,31 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
+          <t>關鍵節點</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
           <t>玩具廠</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>驗收標準（玩具廠）</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>我方（電路板、韌體、App）</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>關鍵節點</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>驗收標準</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="72" customHeight="1">
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>驗收標準（我方）</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="88" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
           <t>W1</t>
@@ -566,26 +572,31 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
+          <t>10/16 全部造型交工廠</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
           <t>收到全部造型後，回覆每個造型的打樣排期</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>書面打樣排期表：每個造型的初樣和第一版樣品日期</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
         <is>
           <t>定下全部 IP 造型交玩具廠（目前只交了馬會）；交機芯規格；向電路板供應商詢價、追加樣板</t>
         </is>
       </c>
-      <c r="E5" s="6" t="inlineStr">
-        <is>
-          <t>10/16 全部造型交工廠</t>
-        </is>
-      </c>
-      <c r="F5" s="7" t="inlineStr">
-        <is>
-          <t>馬會兩款、政協青年聯會版、AI Buddy（如 1/15 出貨）的造型圖（正、側、背面，尺寸，顏色）全部交到工廠；工廠回覆打樣排期</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="40" customHeight="1">
+      <c r="G5" s="7" t="inlineStr">
+        <is>
+          <t>馬會兩款、政協青年聯會版、AI Buddy（如 1/15 出貨）的造型圖（正、側、背面，尺寸，顏色）和機芯規格全部交到工廠；50 片樣板已下單</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="56" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
           <t>W2</t>
@@ -596,20 +607,29 @@
           <t>10/19–10/23</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="C6" s="8" t="inlineStr"/>
+      <c r="D6" s="6" t="inlineStr">
         <is>
           <t>機芯盒 3D 設計、第一版初樣</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>機芯盒 3D 圖和每個造型的初樣照片交我方</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
         <is>
           <t>審 3D 圖；決定電路板改不改；定好 App 和網頁的對接方式</t>
         </is>
       </c>
-      <c r="E6" s="8" t="inlineStr"/>
-      <c r="F6" s="5" t="inlineStr"/>
-    </row>
-    <row r="7" ht="56" customHeight="1">
+      <c r="G6" s="7" t="inlineStr">
+        <is>
+          <t>2 個工作天內回覆 3D 圖意見；改不改板有書面結論；對接清單由做殼的同事確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="72" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
         <is>
           <t>W3</t>
@@ -622,26 +642,31 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
+          <t>10/30 第一版樣品測試</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
           <t>寄出第一版樣品（每款 3 隻）</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>裝板實測，給修改意見；電路板定案</t>
-        </is>
-      </c>
-      <c r="E7" s="6" t="inlineStr">
-        <is>
-          <t>10/30 第一版樣品測試</t>
-        </is>
-      </c>
-      <c r="F7" s="7" t="inlineStr">
-        <is>
-          <t>收音（1 米）、喇叭響度、按鍵、Wi-Fi、充電、跌落全部測過；修改意見已交工廠</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="40" customHeight="1">
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>按「樣品測試項目」自檢後寄出，10/28 前送到我方</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>裝板實測，給修改意見；電路板定案；App 登入和品牌主題</t>
+        </is>
+      </c>
+      <c r="G7" s="7" t="inlineStr">
+        <is>
+          <t>收音、喇叭響度、按鍵、Wi-Fi、充電、跌落全部測過，修改意見 10/30 前交工廠；電路板連續對話 2 小時不當機</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="88" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
           <t>W4</t>
@@ -654,26 +679,31 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
+          <t>11/6 電路板下單</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
           <t>第二版樣品；機芯盒開模；20 隻測試樣品</t>
         </is>
       </c>
-      <c r="D8" s="5" t="inlineStr">
-        <is>
-          <t>量產電路板下單；內部測試開始；App 開發</t>
-        </is>
-      </c>
-      <c r="E8" s="6" t="inlineStr">
-        <is>
-          <t>11/6 電路板下單</t>
-        </is>
-      </c>
-      <c r="F8" s="7" t="inlineStr">
-        <is>
-          <t>3,000 台加備品已下單，供應商確認 12/4 前到廠</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="40" customHeight="1">
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>第二版改好上一輪全部意見；開模排期確認；20 隻測試樣品交我方</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>量產電路板下單；內部測試開始；AI Buddy App 可以內部測試</t>
+        </is>
+      </c>
+      <c r="G8" s="7" t="inlineStr">
+        <is>
+          <t>3,000 台加備品已下單，供應商確認 12/4 前到廠；20 台內部測試機在用；AI Buddy App 在 iPhone、Android 上 10 分鐘內完成配網和綁定</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="56" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
         <is>
           <t>W5</t>
@@ -686,26 +716,31 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
+          <t>11/13 外觀簽樣</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
           <t>外觀簽樣；訂面料和配件</t>
         </is>
       </c>
-      <c r="D9" s="5" t="inlineStr">
-        <is>
-          <t>客戶確認外觀；App 開發</t>
-        </is>
-      </c>
-      <c r="E9" s="6" t="inlineStr">
-        <is>
-          <t>11/13 外觀簽樣</t>
-        </is>
-      </c>
-      <c r="F9" s="7" t="inlineStr">
-        <is>
-          <t>款式 A 兩個造型、款式 B 由客戶書面簽樣；簽樣品雙方各留一隻</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="40" customHeight="1">
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>簽樣品雙方各留一隻；長交期物料已下單，交期在 12/4 前</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>客戶確認外觀；出廠韌體底層凍結</t>
+        </is>
+      </c>
+      <c r="G9" s="7" t="inlineStr">
+        <is>
+          <t>款式 A 兩個造型、款式 B 由客戶書面簽樣；分區表和加密流程凍結</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="56" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
           <t>W6</t>
@@ -718,26 +753,31 @@
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
+          <t>11/20 款式 A 兩款數量</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
           <t>T1 試模；包裝打樣</t>
         </is>
       </c>
-      <c r="D10" s="5" t="inlineStr">
-        <is>
-          <t>成品送檢（玩具安全、無線、電池）；App 開發</t>
-        </is>
-      </c>
-      <c r="E10" s="6" t="inlineStr">
-        <is>
-          <t>11/20 款式 A 兩款數量</t>
-        </is>
-      </c>
-      <c r="F10" s="7" t="inlineStr">
-        <is>
-          <t>客戶書面確認兩個造型各多少</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="40" customHeight="1">
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>T1 機芯盒裝得進電路板、電池、喇叭，按鍵和開孔位置正確；包裝打樣交我方</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>成品送檢；快活和政協青年聯會 App 頁面</t>
+        </is>
+      </c>
+      <c r="G10" s="7" t="inlineStr">
+        <is>
+          <t>玩具安全、無線、電池已送檢；客戶書面確認款式 A 兩款各多少；三個 App 有可以安裝的測試版</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="56" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
         <is>
           <t>W7</t>
@@ -750,26 +790,31 @@
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
+          <t>11/27 產前樣、大貨單</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
           <t>產前樣；包裝定稿</t>
         </is>
       </c>
-      <c r="D11" s="5" t="inlineStr">
-        <is>
-          <t>確認產前樣、下大貨單；出廠韌體交電路板供應商；App 測試版</t>
-        </is>
-      </c>
-      <c r="E11" s="6" t="inlineStr">
-        <is>
-          <t>11/27 產前樣、大貨單</t>
-        </is>
-      </c>
-      <c r="F11" s="7" t="inlineStr">
-        <is>
-          <t>產前樣雙方簽字；大貨單已發出；三個 App 測試版可以安裝使用</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="40" customHeight="1">
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>產前樣和簽樣品一致，「樣品測試項目」全部合格；包裝稿雙方確認</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>確認產前樣、下大貨單；出廠韌體交電路板供應商；App 功能凍結</t>
+        </is>
+      </c>
+      <c r="G11" s="7" t="inlineStr">
+        <is>
+          <t>產前樣雙方簽字；大貨單已發出；出廠韌體已交；三個 App 全流程在 iOS、Android 各兩款手機通過</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="56" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
           <t>W8</t>
@@ -782,26 +827,31 @@
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
+          <t>11/30 App 送審</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
           <t>物料和電路板到廠，排產線</t>
         </is>
       </c>
-      <c r="D12" s="5" t="inlineStr">
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>物料和電路板點數無缺；生產排期表交我方</t>
+        </is>
+      </c>
+      <c r="F12" s="6" t="inlineStr">
         <is>
           <t>交燒錄自檢工位和作業指導書；App 提交蘋果和 Google 審核</t>
         </is>
       </c>
-      <c r="E12" s="6" t="inlineStr">
-        <is>
-          <t>11/30 App 送審</t>
-        </is>
-      </c>
-      <c r="F12" s="7" t="inlineStr">
-        <is>
-          <t>三個 App 已提交審核</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="40" customHeight="1">
+      <c r="G12" s="7" t="inlineStr">
+        <is>
+          <t>工位在工廠試跑 10 台全部通過；三個 App 已提交，上架資料齊全</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="56" customHeight="1">
       <c r="A13" s="4" t="inlineStr">
         <is>
           <t>W9</t>
@@ -814,26 +864,31 @@
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
+          <t>12/11 試產、App 過審</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
           <t>試產 50–100 隻</t>
         </is>
       </c>
-      <c r="D13" s="5" t="inlineStr">
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>全檢合格，發現的問題已改好</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="inlineStr">
         <is>
           <t>全檢試產品；App 審核（預留被拒重交的時間）</t>
         </is>
       </c>
-      <c r="E13" s="6" t="inlineStr">
-        <is>
-          <t>12/11 試產、App 過審</t>
-        </is>
-      </c>
-      <c r="F13" s="7" t="inlineStr">
-        <is>
-          <t>試產全檢合格，問題已改好；三個 App 通過審核；檢測報告合格</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="40" customHeight="1">
+      <c r="G13" s="7" t="inlineStr">
+        <is>
+          <t>試產品配網、對話、充電全部測過；三個 App 通過審核；檢測報告合格</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="56" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
         <is>
           <t>W10</t>
@@ -846,20 +901,29 @@
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>大貨開始，每日回報產量和不良率</t>
-        </is>
-      </c>
-      <c r="D14" s="5" t="inlineStr">
+          <t>12/14 大貨開始</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>大貨開始</t>
+        </is>
+      </c>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>每天回報產量和不良率</t>
+        </is>
+      </c>
+      <c r="F14" s="6" t="inlineStr">
         <is>
           <t>App 上架但不公開，客戶驗收</t>
         </is>
       </c>
-      <c r="E14" s="6" t="inlineStr">
-        <is>
-          <t>12/14 大貨開始</t>
-        </is>
-      </c>
-      <c r="F14" s="7" t="inlineStr"/>
+      <c r="G14" s="7" t="inlineStr">
+        <is>
+          <t>客戶書面確認 App；3 位非團隊成員從開箱到第一次對話都在 10 分鐘內完成</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="40" customHeight="1">
       <c r="A15" s="4" t="inlineStr">
@@ -872,18 +936,27 @@
           <t>12/21–12/25</t>
         </is>
       </c>
-      <c r="C15" s="5" t="inlineStr">
-        <is>
-          <t>大貨生產；中期驗貨</t>
-        </is>
-      </c>
-      <c r="D15" s="5" t="inlineStr">
-        <is>
-          <t>12/25–26 香港假期</t>
-        </is>
-      </c>
-      <c r="E15" s="8" t="inlineStr"/>
-      <c r="F15" s="5" t="inlineStr"/>
+      <c r="C15" s="8" t="inlineStr"/>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>大貨生產</t>
+        </is>
+      </c>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>產量按排期進行</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>中期驗貨（12/25–26 香港假期）</t>
+        </is>
+      </c>
+      <c r="G15" s="7" t="inlineStr">
+        <is>
+          <t>中期驗貨抽檢合格</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="24" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
@@ -898,24 +971,25 @@
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
+          <t>12/31 大貨完成</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
           <t>大貨完成</t>
         </is>
       </c>
-      <c r="D16" s="5" t="inlineStr">
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>全部數量完成</t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="inlineStr">
         <is>
           <t>1/1 假期</t>
         </is>
       </c>
-      <c r="E16" s="6" t="inlineStr">
-        <is>
-          <t>12/31 大貨完成</t>
-        </is>
-      </c>
-      <c r="F16" s="7" t="inlineStr">
-        <is>
-          <t>全部數量完成；中期驗貨合格</t>
-        </is>
-      </c>
+      <c r="G16" s="6" t="inlineStr"/>
     </row>
     <row r="17" ht="40" customHeight="1">
       <c r="A17" s="4" t="inlineStr">
@@ -928,18 +1002,27 @@
           <t>1/4–1/8</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr">
-        <is>
-          <t>緩衝週：返工、補貨；尾期驗貨</t>
-        </is>
-      </c>
-      <c r="D17" s="5" t="inlineStr">
-        <is>
-          <t>客戶確認 App 公開日期</t>
-        </is>
-      </c>
-      <c r="E17" s="8" t="inlineStr"/>
-      <c r="F17" s="5" t="inlineStr"/>
+      <c r="C17" s="8" t="inlineStr"/>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>緩衝週：返工、補貨</t>
+        </is>
+      </c>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>返工和補貨全部完成</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>尾期驗貨；客戶確認 App 公開日期</t>
+        </is>
+      </c>
+      <c r="G17" s="7" t="inlineStr">
+        <is>
+          <t>尾期驗貨（AQL）合格</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="40" customHeight="1">
       <c r="A18" s="4" t="inlineStr">
@@ -954,22 +1037,27 @@
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
+          <t>1/15 出貨</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
           <t>包裝、裝箱、出貨</t>
         </is>
       </c>
-      <c r="D18" s="5" t="inlineStr">
-        <is>
-          <t>App 公開上架</t>
-        </is>
-      </c>
-      <c r="E18" s="6" t="inlineStr">
-        <is>
-          <t>1/15 出貨</t>
-        </is>
-      </c>
-      <c r="F18" s="7" t="inlineStr">
-        <is>
-          <t>尾期驗貨合格；出貨清單和序號／MAC 對照表；每台已在系統登記</t>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>出貨清單和序號／MAC 對照表交我方</t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t>App 公開上架；確認設備登記</t>
+        </is>
+      </c>
+      <c r="G18" s="7" t="inlineStr">
+        <is>
+          <t>每台都已在系統登記；三個 App 公開</t>
         </is>
       </c>
     </row>
@@ -984,18 +1072,19 @@
           <t>1/18–1/29</t>
         </is>
       </c>
-      <c r="C19" s="5" t="inlineStr"/>
-      <c r="D19" s="5" t="inlineStr">
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>1/29 送達</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr"/>
+      <c r="E19" s="6" t="inlineStr"/>
+      <c r="F19" s="6" t="inlineStr">
         <is>
           <t>運送、簽收</t>
         </is>
       </c>
-      <c r="E19" s="6" t="inlineStr">
-        <is>
-          <t>1/29 送達</t>
-        </is>
-      </c>
-      <c r="F19" s="7" t="inlineStr">
+      <c r="G19" s="7" t="inlineStr">
         <is>
           <t>全部簽收</t>
         </is>
@@ -1004,7 +1093,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>黃色格是關鍵節點和驗收標準：延誤的話，後面的日期會跟著推遲，請提早通知。</t>
+          <t>黃色格是關鍵節點和驗收標準。關鍵節點延誤的話，後面的日期會跟著推遲，請提早通知。</t>
         </is>
       </c>
     </row>
@@ -1017,10 +1106,10 @@
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A21:F21"/>
-    <mergeCell ref="A22:F22"/>
-    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A21:G21"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A22:G22"/>
+    <mergeCell ref="A1:G1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
@@ -1094,7 +1183,7 @@
           <t>對接方案定案</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D5" s="6" t="inlineStr">
         <is>
           <t>① 網頁和殼的對接清單：藍牙配網、原生登入、推送、麥克風、刪除帳號、深層連結，每項寫明介面、參數、回傳和錯誤
 ② 做殼的同事書面確認
@@ -1118,7 +1207,7 @@
           <t>登入和品牌主題</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="D6" s="6" t="inlineStr">
         <is>
           <t>① email 驗證碼登入可用；Google／Apple 登入由殼完成，網頁收得到登入結果
 ② App 內可以刪除帳號
@@ -1142,7 +1231,7 @@
           <t>AI Buddy App 可以內部測試</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="D7" s="6" t="inlineStr">
         <is>
           <t>① iPhone 和 Android 都能用藍牙找到玩具、選 Wi-Fi、完成綁定，10 分鐘內做完
 ② 選角色、對話、改設定、解綁都正常
@@ -1166,7 +1255,7 @@
           <t>快活和政協青年聯會 App 頁面完成</t>
         </is>
       </c>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="D8" s="6" t="inlineStr">
         <is>
           <t>① 快活：會員綁定、查看記憶、一鍵忘記、選語言（粵／普／英）
 ② 政協青年聯會版：品牌頁面和角色
@@ -1190,7 +1279,7 @@
           <t>功能凍結</t>
         </is>
       </c>
-      <c r="D9" s="5" t="inlineStr">
+      <c r="D9" s="6" t="inlineStr">
         <is>
           <t>① 三個 App 全流程通過：安裝 → 登入 → 藍牙配網 → 綁定 → 對話 → 解綁；iOS 和 Android 各至少兩款手機
 ② Wi-Fi 密碼錯、玩具已被別人綁定、斷網時都有清楚提示
@@ -1215,7 +1304,7 @@
           <t>提交商店審核</t>
         </is>
       </c>
-      <c r="D10" s="5" t="inlineStr">
+      <c r="D10" s="6" t="inlineStr">
         <is>
           <t>① 上架資料齊全：截圖、描述、私隱政策網址、私隱標籤、審核用測試帳號、玩具示範影片
 ② 三個 App 已提交蘋果和 Google</t>
@@ -1238,7 +1327,7 @@
           <t>通過審核</t>
         </is>
       </c>
-      <c r="D11" s="5" t="inlineStr">
+      <c r="D11" s="6" t="inlineStr">
         <is>
           <t>① 三個 App 都通過蘋果和 Google 審核
 ② 如果被拒，修改後重交並通過</t>
@@ -1261,7 +1350,7 @@
           <t>客戶驗收</t>
         </is>
       </c>
-      <c r="D12" s="5" t="inlineStr">
+      <c r="D12" s="6" t="inlineStr">
         <is>
           <t>① 馬會、政協青年聯會用正式版走一次完整流程，書面確認
 ② 找 3 位非團隊成員，從開箱到第一次對話都在 10 分鐘內完成
@@ -1285,7 +1374,7 @@
           <t>公開上架</t>
         </is>
       </c>
-      <c r="D13" s="5" t="inlineStr">
+      <c r="D13" s="6" t="inlineStr">
         <is>
           <t>① 三個 App 公開，用戶搜尋得到
 ② App 內看得到客服聯絡方式、常見問題、保修條款</t>
@@ -1363,7 +1452,7 @@
           <t>收音</t>
         </is>
       </c>
-      <c r="B2" s="5" t="inlineStr">
+      <c r="B2" s="6" t="inlineStr">
         <is>
           <t>距離 1 米正常說話，語音識別正確；和裸板比較不能明顯變差</t>
         </is>
@@ -1380,7 +1469,7 @@
           <t>喇叭</t>
         </is>
       </c>
-      <c r="B3" s="5" t="inlineStr">
+      <c r="B3" s="6" t="inlineStr">
         <is>
           <t>隔著布料的響度和清晰度；最大音量不破音、不震動</t>
         </is>
@@ -1397,7 +1486,7 @@
           <t>按鍵</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="6" t="inlineStr">
         <is>
           <t>隔著布料／徽章按得到，小朋友按得動，回彈清楚</t>
         </is>
@@ -1414,7 +1503,7 @@
           <t>Wi-Fi</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="6" t="inlineStr">
         <is>
           <t>裝進公仔後訊號強度，和裸板比較</t>
         </is>
@@ -1431,7 +1520,7 @@
           <t>充電</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B6" s="6" t="inlineStr">
         <is>
           <t>USB-C 插得進，充電時燈號看得到</t>
         </is>
@@ -1448,7 +1537,7 @@
           <t>燈號</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B7" s="6" t="inlineStr">
         <is>
           <t>低電紅燈從外面看得到（或確定不外露）</t>
         </is>
@@ -1465,7 +1554,7 @@
           <t>跌落</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B8" s="6" t="inlineStr">
         <is>
           <t>1 米跌落，零件不脫落，機芯盒不鬆脫</t>
         </is>
@@ -1482,7 +1571,7 @@
           <t>小零件與尖角</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B9" s="6" t="inlineStr">
         <is>
           <t>眼睛、徽章、配件拉力測試；沒有尖角和可吞食的小零件</t>
         </is>
@@ -1499,7 +1588,7 @@
           <t>拆裝</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B10" s="6" t="inlineStr">
         <is>
           <t>機芯盒能取出維修，縫口或拉鍊位置合理</t>
         </is>

--- a/docs/毛公仔打版與量產時間表_草案v0.5.xlsx
+++ b/docs/毛公仔打版與量產時間表_草案v0.5.xlsx
@@ -8,11 +8,12 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="時間表" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="App 開發與上架" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="軟件開發與測試" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="樣品測試項目" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'時間表'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'軟件開發與測試'!$4:$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -82,7 +83,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -104,11 +105,44 @@
         <color rgb="00C9CED6"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C9CED6"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C9CED6"/>
+      </left>
+      <right style="thin">
+        <color rgb="00C9CED6"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C9CED6"/>
+      </left>
+      <right style="thin">
+        <color rgb="00C9CED6"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00C9CED6"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -131,6 +165,11 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -777,7 +816,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="56" customHeight="1">
+    <row r="11" ht="72" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
         <is>
           <t>W7</t>
@@ -805,7 +844,7 @@
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
-          <t>確認產前樣、下大貨單；出廠韌體交電路板供應商；App 功能凍結</t>
+          <t>確認產前樣、下大貨單；出廠韌體交電路板供應商；網頁和 App 功能凍結，系統測試開始</t>
         </is>
       </c>
       <c r="G11" s="7" t="inlineStr">
@@ -842,12 +881,12 @@
       </c>
       <c r="F12" s="6" t="inlineStr">
         <is>
-          <t>交燒錄自檢工位和作業指導書；App 提交蘋果和 Google 審核</t>
+          <t>交燒錄自檢工位和作業指導書；App 提交蘋果和 Google 審核；系統測試</t>
         </is>
       </c>
       <c r="G12" s="7" t="inlineStr">
         <is>
-          <t>工位在工廠試跑 10 台全部通過；三個 App 已提交，上架資料齊全</t>
+          <t>工位在工廠試跑 10 台全部通過；三個 App 已提交，上架資料齊全；系統測試和壓測通過</t>
         </is>
       </c>
     </row>
@@ -879,7 +918,7 @@
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
-          <t>全檢試產品；App 審核（預留被拒重交的時間）</t>
+          <t>全檢試產品；App 審核（預留被拒重交的時間）；客戶 UAT 開始</t>
         </is>
       </c>
       <c r="G13" s="7" t="inlineStr">
@@ -916,12 +955,12 @@
       </c>
       <c r="F14" s="6" t="inlineStr">
         <is>
-          <t>App 上架但不公開，客戶驗收</t>
+          <t>客戶 UAT 完成；App 上架但不公開</t>
         </is>
       </c>
       <c r="G14" s="7" t="inlineStr">
         <is>
-          <t>客戶書面確認 App；3 位非團隊成員從開箱到第一次對話都在 10 分鐘內完成</t>
+          <t>客戶 UAT 書面簽收，嚴重問題 0 個；3 位非團隊成員從開箱到第一次對話都在 10 分鐘內完成</t>
         </is>
       </c>
     </row>
@@ -1122,269 +1161,533 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:E23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="70" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="64" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="9" t="inlineStr">
         <is>
-          <t>App 開發與上架：里程碑和驗收標準</t>
+          <t>軟件開發與測試：網頁、App、Tool call、RAG、後台、測試、UAT</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>網頁 App 包在原生殼裡，三個品牌各一個 App。殼過審後，網頁畫面可以繼續更新，不用重新送審。</t>
+          <t>網頁 App 包在原生殼裡，三個品牌各一個 App、各一套系統。殼過審後，網頁畫面可以繼續更新，不用重新送審。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
+          <t>工作線</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
           <t>週次</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>日期</t>
-        </is>
-      </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>里程碑</t>
+          <t>完成日期</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
+          <t>內容</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
           <t>驗收標準（全部做到才算完成）</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="72" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>W2</t>
+    <row r="5" ht="56" customHeight="1">
+      <c r="A5" s="10" t="inlineStr">
+        <is>
+          <t>網頁</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
+          <t>W1–W3</t>
+        </is>
+      </c>
+      <c r="C5" s="10" t="inlineStr">
+        <is>
+          <t>10/30</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>共用基礎：品牌主題、App 內登入、刪除帳號</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>三個品牌的顏色、logo、文案顯示正確，畫面不閃；email 驗證碼登入、Google／Apple 登入（由殼完成）、App 內刪除帳號都可用</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="40" customHeight="1">
+      <c r="A6" s="11" t="n"/>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>W3–W4</t>
+        </is>
+      </c>
+      <c r="C6" s="10" t="inlineStr">
+        <is>
+          <t>11/6</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>AI Buddy 網頁：配網、綁定、角色、設定、家長控制</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>iPhone 和 Android 上 10 分鐘內完成藍牙配網和綁定；選角色、對話、改設定、解綁、家長鎖、每日上限都正常</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="40" customHeight="1">
+      <c r="A7" s="11" t="n"/>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>W4–W6</t>
+        </is>
+      </c>
+      <c r="C7" s="10" t="inlineStr">
+        <is>
+          <t>11/20</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>快活和政協青年聯會網頁</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>快活：會員綁定、查看記憶、一鍵忘記、選語言（粵／普／英）；政協青年聯會版：品牌頁面和角色</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="56" customHeight="1">
+      <c r="A8" s="12" t="n"/>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>W7</t>
+        </is>
+      </c>
+      <c r="C8" s="10" t="inlineStr">
+        <is>
+          <t>11/27</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>功能凍結</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>三個品牌全流程通過：安裝 → 登入 → 配網 → 綁定 → 對話 → 解綁，iOS 和 Android 各至少兩款手機；Wi-Fi 密碼錯、玩具已被綁定、斷網時都有清楚提示</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="56" customHeight="1">
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>App 殼與上架</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>W1–W2</t>
+        </is>
+      </c>
+      <c r="C9" s="10" t="inlineStr">
+        <is>
           <t>10/23</t>
         </is>
       </c>
-      <c r="C5" s="8" t="inlineStr">
-        <is>
-          <t>對接方案定案</t>
-        </is>
-      </c>
-      <c r="D5" s="6" t="inlineStr">
-        <is>
-          <t>① 網頁和殼的對接清單：藍牙配網、原生登入、推送、麥克風、刪除帳號、深層連結，每項寫明介面、參數、回傳和錯誤
-② 做殼的同事書面確認
-③ 三個 App 的名稱、圖示、bundle id 定好</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="72" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>W3</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>網頁和殼的對接方案</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>對接清單（藍牙配網、原生登入、推送、麥克風、刪除帳號、深層連結）逐項寫明介面和錯誤，做殼的同事書面確認；三個 App 的名稱、圖示、bundle id 定好</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="56" customHeight="1">
+      <c r="A10" s="11" t="n"/>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>W3–W6</t>
+        </is>
+      </c>
+      <c r="C10" s="10" t="inlineStr">
+        <is>
+          <t>11/20</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>殼開發、測試版</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>三個 App 的測試版可以安裝（TestFlight、Google 內部測試）；藍牙、登入、推送（玩具上線、低電）可用；連續使用 30 分鐘不閃退</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="56" customHeight="1">
+      <c r="A11" s="11" t="n"/>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>W8–W9</t>
+        </is>
+      </c>
+      <c r="C11" s="10" t="inlineStr">
+        <is>
+          <t>12/11</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>提交審核、通過審核</t>
+        </is>
+      </c>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>11/30 提交，上架資料齊全（截圖、私隱政策、私隱標籤、審核用帳號、玩具示範影片）；12/11 前三個 App 通過蘋果和 Google 審核</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="40" customHeight="1">
+      <c r="A12" s="12" t="n"/>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>W14</t>
+        </is>
+      </c>
+      <c r="C12" s="10" t="inlineStr">
+        <is>
+          <t>1/15</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>公開上架</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>三個 App 公開，用戶搜尋得到；App 內看得到客服、常見問題、保修條款</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="56" customHeight="1">
+      <c r="A13" s="10" t="inlineStr">
+        <is>
+          <t>Tool call</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>W2–W3</t>
+        </is>
+      </c>
+      <c r="C13" s="10" t="inlineStr">
         <is>
           <t>10/30</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
-        <is>
-          <t>登入和品牌主題</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="inlineStr">
-        <is>
-          <t>① email 驗證碼登入可用；Google／Apple 登入由殼完成，網頁收得到登入結果
-② App 內可以刪除帳號
-③ 三個品牌各自的顏色、logo、文案顯示正確，畫面不閃</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="72" customHeight="1">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>工具清單和設計</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>定好語音助手可以調用的工具（建議：天氣、日期和節日、調音量、結束對話、快活的賽事資料查詢），每個工具的觸發說法和回覆方式，以及每個品牌允許哪些工具</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="40" customHeight="1">
+      <c r="A14" s="12" t="n"/>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>W4–W6</t>
+        </is>
+      </c>
+      <c r="C14" s="10" t="inlineStr">
+        <is>
+          <t>11/20</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>開發和測試</t>
+        </is>
+      </c>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>每個工具用真實語音觸發 20 次，成功率 ≥ 95%；不相關的話不會誤觸發；首字延遲增加不超過 300 毫秒</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="24" customHeight="1">
+      <c r="A15" s="10" t="inlineStr">
+        <is>
+          <t>RAG 知識庫（快活）</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>W4</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="C15" s="10" t="inlineStr">
         <is>
           <t>11/6</t>
         </is>
       </c>
-      <c r="C7" s="8" t="inlineStr">
-        <is>
-          <t>AI Buddy App 可以內部測試</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="inlineStr">
-        <is>
-          <t>① iPhone 和 Android 都能用藍牙找到玩具、選 Wi-Fi、完成綁定，10 分鐘內做完
-② 選角色、對話、改設定、解綁都正常
-③ 家長控制（家長鎖、每日上限）可用</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="56" customHeight="1">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>W6</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>收資料、入庫流程</t>
+        </is>
+      </c>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>馬會第一批資料已收到；入庫、版本、審批流程跑通一次</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="40" customHeight="1">
+      <c r="A16" s="11" t="n"/>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>W5–W8</t>
+        </is>
+      </c>
+      <c r="C16" s="10" t="inlineStr">
+        <is>
+          <t>12/4</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>檢索和回答</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>100 條測試問題答對率 ≥ 90%；知識庫沒有的內容會說不肯定並建議查詢；問貼士、賠率、賽果預測 100% 婉拒</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="40" customHeight="1">
+      <c r="A17" s="12" t="n"/>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>W9–W11</t>
+        </is>
+      </c>
+      <c r="C17" s="10" t="inlineStr">
+        <is>
+          <t>12/25</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>馬會審核 v1</t>
+        </is>
+      </c>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>馬會書面批准 v1；每一版都有審批記錄；更新知識庫不用重新燒錄玩具</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="56" customHeight="1">
+      <c r="A18" s="10" t="inlineStr">
+        <is>
+          <t>後台管理</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>W3–W6</t>
+        </is>
+      </c>
+      <c r="C18" s="10" t="inlineStr">
         <is>
           <t>11/20</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
-        <is>
-          <t>快活和政協青年聯會 App 頁面完成</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>① 快活：會員綁定、查看記憶、一鍵忘記、選語言（粵／普／英）
-② 政協青年聯會版：品牌頁面和角色
-③ 三個 App 都有測試版可以安裝（TestFlight、Google 內部測試）</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="88" customHeight="1">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>W7</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>管理功能</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>內容管理員：上載知識庫並送審、發佈角色；超級管理員：看設備最後上線、韌體版本、錯誤，發佈 OTA，解綁和換機；任何管理員都看不到對話內容</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="40" customHeight="1">
+      <c r="A19" s="12" t="n"/>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>W6–W8</t>
+        </is>
+      </c>
+      <c r="C19" s="10" t="inlineStr">
+        <is>
+          <t>12/4</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>三個品牌各自一套系統</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>三套各自上線，冒煙測試（登入、對話、OTA 檢查）通過；部署腳本一次跑完三套；一套停機不影響另外兩套</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="40" customHeight="1">
+      <c r="A20" s="10" t="inlineStr">
+        <is>
+          <t>測試</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>W4–W7</t>
+        </is>
+      </c>
+      <c r="C20" s="10" t="inlineStr">
         <is>
           <t>11/27</t>
         </is>
       </c>
-      <c r="C9" s="8" t="inlineStr">
-        <is>
-          <t>功能凍結</t>
-        </is>
-      </c>
-      <c r="D9" s="6" t="inlineStr">
-        <is>
-          <t>① 三個 App 全流程通過：安裝 → 登入 → 藍牙配網 → 綁定 → 對話 → 解綁；iOS 和 Android 各至少兩款手機
-② Wi-Fi 密碼錯、玩具已被別人綁定、斷網時都有清楚提示
-③ 推送收得到：玩具第一次上線、低電提醒
-④ 連續使用 30 分鐘不閃退</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="56" customHeight="1">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>W8</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>11/30</t>
-        </is>
-      </c>
-      <c r="C10" s="8" t="inlineStr">
-        <is>
-          <t>提交商店審核</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="inlineStr">
-        <is>
-          <t>① 上架資料齊全：截圖、描述、私隱政策網址、私隱標籤、審核用測試帳號、玩具示範影片
-② 三個 App 已提交蘋果和 Google</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="40" customHeight="1">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>W9</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>12/11</t>
-        </is>
-      </c>
-      <c r="C11" s="8" t="inlineStr">
-        <is>
-          <t>通過審核</t>
-        </is>
-      </c>
-      <c r="D11" s="6" t="inlineStr">
-        <is>
-          <t>① 三個 App 都通過蘋果和 Google 審核
-② 如果被拒，修改後重交並通過</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="56" customHeight="1">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>W10</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>內部測試（20 台、4 週）</t>
+        </is>
+      </c>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>每週記錄對話輪數、首字延遲、每台成本、安全事件；第 4 週出測試報告</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="40" customHeight="1">
+      <c r="A21" s="12" t="n"/>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>W7–W8</t>
+        </is>
+      </c>
+      <c r="C21" s="10" t="inlineStr">
+        <is>
+          <t>12/4</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>系統測試</t>
+        </is>
+      </c>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>全流程測試通過；按 3,000 台規模壓測（150–300 個同時對話）通過；安全測試通過；嚴重問題 0 個</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="56" customHeight="1">
+      <c r="A22" s="10" t="inlineStr">
+        <is>
+          <t>UAT</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>W9–W10</t>
+        </is>
+      </c>
+      <c r="C22" s="10" t="inlineStr">
         <is>
           <t>12/18</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
-        <is>
-          <t>客戶驗收</t>
-        </is>
-      </c>
-      <c r="D12" s="6" t="inlineStr">
-        <is>
-          <t>① 馬會、政協青年聯會用正式版走一次完整流程，書面確認
-② 找 3 位非團隊成員，從開箱到第一次對話都在 10 分鐘內完成
-③ App 已上架但不公開</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="40" customHeight="1">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>W14</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>1/15</t>
-        </is>
-      </c>
-      <c r="C13" s="8" t="inlineStr">
-        <is>
-          <t>公開上架</t>
-        </is>
-      </c>
-      <c r="D13" s="6" t="inlineStr">
-        <is>
-          <t>① 三個 App 公開，用戶搜尋得到
-② App 內看得到客服聯絡方式、常見問題、保修條款</t>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>客戶 UAT（用試產機和正式版 App）</t>
+        </is>
+      </c>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t>按 UAT 清單逐項測完；馬會、政協青年聯會書面簽收；嚴重問題 0 個，其他問題都有處理日期；3 位非團隊成員從開箱到第一次對話都在 10 分鐘內完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="40" customHeight="1">
+      <c r="A23" s="12" t="n"/>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>W13</t>
+        </is>
+      </c>
+      <c r="C23" s="10" t="inlineStr">
+        <is>
+          <t>1/8</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>上線前最後確認</t>
+        </is>
+      </c>
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t>UAT 遺留問題全部處理；正式環境凍結，只修 bug；監控和告警正常</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A2:D2"/>
+  <mergeCells count="9">
+    <mergeCell ref="A9:A12"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="A15:A17"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="A5:A8"/>
+    <mergeCell ref="A18:A19"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>

--- a/docs/毛公仔打版與量產時間表_草案v0.5.xlsx
+++ b/docs/毛公仔打版與量產時間表_草案v0.5.xlsx
@@ -659,12 +659,12 @@
       </c>
       <c r="F6" s="6" t="inlineStr">
         <is>
-          <t>審 3D 圖；決定電路板改不改；定好 App 和網頁的對接方式</t>
+          <t>審 3D 圖；決定電路板改不改；和 Neo 定好 App 殼和網頁的對接方式</t>
         </is>
       </c>
       <c r="G6" s="7" t="inlineStr">
         <is>
-          <t>2 個工作天內回覆 3D 圖意見；改不改板有書面結論；對接清單由做殼的同事確認</t>
+          <t>2 個工作天內回覆 3D 圖意見；改不改板有書面結論；對接清單由 Neo 確認</t>
         </is>
       </c>
     </row>
@@ -881,7 +881,7 @@
       </c>
       <c r="F12" s="6" t="inlineStr">
         <is>
-          <t>交燒錄自檢工位和作業指導書；App 提交蘋果和 Google 審核；系統測試</t>
+          <t>交燒錄自檢工位和作業指導書；Neo 提交三個 App 給蘋果和 Google 審核；系統測試</t>
         </is>
       </c>
       <c r="G12" s="7" t="inlineStr">
@@ -1161,14 +1161,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E23"/>
+  <dimension ref="A1:F23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
-    <col width="64" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
+    <col width="60" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1181,7 +1182,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>網頁 App 包在原生殼裡，三個品牌各一個 App、各一套系統。殼過審後，網頁畫面可以繼續更新，不用重新送審。</t>
+          <t>網頁 App 包在原生殼裡，三個品牌各一個 App、各一套系統。殼由 Neo 負責；「我方軟件」是網頁、後台、語音系統和韌體。殼過審後，網頁畫面可以繼續更新，不用重新送審。</t>
         </is>
       </c>
     </row>
@@ -1203,10 +1204,15 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
+          <t>負責</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
           <t>內容</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>驗收標準（全部做到才算完成）</t>
         </is>
@@ -1228,12 +1234,17 @@
           <t>10/30</t>
         </is>
       </c>
-      <c r="D5" s="6" t="inlineStr">
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>我方軟件</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
         <is>
           <t>共用基礎：品牌主題、App 內登入、刪除帳號</t>
         </is>
       </c>
-      <c r="E5" s="7" t="inlineStr">
+      <c r="F5" s="7" t="inlineStr">
         <is>
           <t>三個品牌的顏色、logo、文案顯示正確，畫面不閃；email 驗證碼登入、Google／Apple 登入（由殼完成）、App 內刪除帳號都可用</t>
         </is>
@@ -1251,12 +1262,17 @@
           <t>11/6</t>
         </is>
       </c>
-      <c r="D6" s="6" t="inlineStr">
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>我方軟件</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
         <is>
           <t>AI Buddy 網頁：配網、綁定、角色、設定、家長控制</t>
         </is>
       </c>
-      <c r="E6" s="7" t="inlineStr">
+      <c r="F6" s="7" t="inlineStr">
         <is>
           <t>iPhone 和 Android 上 10 分鐘內完成藍牙配網和綁定；選角色、對話、改設定、解綁、家長鎖、每日上限都正常</t>
         </is>
@@ -1274,12 +1290,17 @@
           <t>11/20</t>
         </is>
       </c>
-      <c r="D7" s="6" t="inlineStr">
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>我方軟件</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
         <is>
           <t>快活和政協青年聯會網頁</t>
         </is>
       </c>
-      <c r="E7" s="7" t="inlineStr">
+      <c r="F7" s="7" t="inlineStr">
         <is>
           <t>快活：會員綁定、查看記憶、一鍵忘記、選語言（粵／普／英）；政協青年聯會版：品牌頁面和角色</t>
         </is>
@@ -1297,12 +1318,17 @@
           <t>11/27</t>
         </is>
       </c>
-      <c r="D8" s="6" t="inlineStr">
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>我方軟件</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
         <is>
           <t>功能凍結</t>
         </is>
       </c>
-      <c r="E8" s="7" t="inlineStr">
+      <c r="F8" s="7" t="inlineStr">
         <is>
           <t>三個品牌全流程通過：安裝 → 登入 → 配網 → 綁定 → 對話 → 解綁，iOS 和 Android 各至少兩款手機；Wi-Fi 密碼錯、玩具已被綁定、斷網時都有清楚提示</t>
         </is>
@@ -1324,12 +1350,17 @@
           <t>10/23</t>
         </is>
       </c>
-      <c r="D9" s="6" t="inlineStr">
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>Neo、我方軟件</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
         <is>
           <t>網頁和殼的對接方案</t>
         </is>
       </c>
-      <c r="E9" s="7" t="inlineStr">
+      <c r="F9" s="7" t="inlineStr">
         <is>
           <t>對接清單（藍牙配網、原生登入、推送、麥克風、刪除帳號、深層連結）逐項寫明介面和錯誤，做殼的同事書面確認；三個 App 的名稱、圖示、bundle id 定好</t>
         </is>
@@ -1347,12 +1378,17 @@
           <t>11/20</t>
         </is>
       </c>
-      <c r="D10" s="6" t="inlineStr">
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>Neo</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
         <is>
           <t>殼開發、測試版</t>
         </is>
       </c>
-      <c r="E10" s="7" t="inlineStr">
+      <c r="F10" s="7" t="inlineStr">
         <is>
           <t>三個 App 的測試版可以安裝（TestFlight、Google 內部測試）；藍牙、登入、推送（玩具上線、低電）可用；連續使用 30 分鐘不閃退</t>
         </is>
@@ -1370,12 +1406,17 @@
           <t>12/11</t>
         </is>
       </c>
-      <c r="D11" s="6" t="inlineStr">
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>Neo（客戶提供開發者帳號）</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
         <is>
           <t>提交審核、通過審核</t>
         </is>
       </c>
-      <c r="E11" s="7" t="inlineStr">
+      <c r="F11" s="7" t="inlineStr">
         <is>
           <t>11/30 提交，上架資料齊全（截圖、私隱政策、私隱標籤、審核用帳號、玩具示範影片）；12/11 前三個 App 通過蘋果和 Google 審核</t>
         </is>
@@ -1393,12 +1434,17 @@
           <t>1/15</t>
         </is>
       </c>
-      <c r="D12" s="6" t="inlineStr">
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>Neo</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="inlineStr">
         <is>
           <t>公開上架</t>
         </is>
       </c>
-      <c r="E12" s="7" t="inlineStr">
+      <c r="F12" s="7" t="inlineStr">
         <is>
           <t>三個 App 公開，用戶搜尋得到；App 內看得到客服、常見問題、保修條款</t>
         </is>
@@ -1420,12 +1466,17 @@
           <t>10/30</t>
         </is>
       </c>
-      <c r="D13" s="6" t="inlineStr">
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>我方軟件</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
         <is>
           <t>工具清單和設計</t>
         </is>
       </c>
-      <c r="E13" s="7" t="inlineStr">
+      <c r="F13" s="7" t="inlineStr">
         <is>
           <t>定好語音助手可以調用的工具（建議：天氣、日期和節日、調音量、結束對話、快活的賽事資料查詢），每個工具的觸發說法和回覆方式，以及每個品牌允許哪些工具</t>
         </is>
@@ -1443,18 +1494,23 @@
           <t>11/20</t>
         </is>
       </c>
-      <c r="D14" s="6" t="inlineStr">
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>我方軟件</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="inlineStr">
         <is>
           <t>開發和測試</t>
         </is>
       </c>
-      <c r="E14" s="7" t="inlineStr">
+      <c r="F14" s="7" t="inlineStr">
         <is>
           <t>每個工具用真實語音觸發 20 次，成功率 ≥ 95%；不相關的話不會誤觸發；首字延遲增加不超過 300 毫秒</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="24" customHeight="1">
+    <row r="15" ht="40" customHeight="1">
       <c r="A15" s="10" t="inlineStr">
         <is>
           <t>RAG 知識庫（快活）</t>
@@ -1470,12 +1526,17 @@
           <t>11/6</t>
         </is>
       </c>
-      <c r="D15" s="6" t="inlineStr">
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>馬會提供資料；我方軟件</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
         <is>
           <t>收資料、入庫流程</t>
         </is>
       </c>
-      <c r="E15" s="7" t="inlineStr">
+      <c r="F15" s="7" t="inlineStr">
         <is>
           <t>馬會第一批資料已收到；入庫、版本、審批流程跑通一次</t>
         </is>
@@ -1493,12 +1554,17 @@
           <t>12/4</t>
         </is>
       </c>
-      <c r="D16" s="6" t="inlineStr">
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>我方軟件</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="inlineStr">
         <is>
           <t>檢索和回答</t>
         </is>
       </c>
-      <c r="E16" s="7" t="inlineStr">
+      <c r="F16" s="7" t="inlineStr">
         <is>
           <t>100 條測試問題答對率 ≥ 90%；知識庫沒有的內容會說不肯定並建議查詢；問貼士、賠率、賽果預測 100% 婉拒</t>
         </is>
@@ -1516,12 +1582,17 @@
           <t>12/25</t>
         </is>
       </c>
-      <c r="D17" s="6" t="inlineStr">
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>馬會審核；我方軟件修改</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="inlineStr">
         <is>
           <t>馬會審核 v1</t>
         </is>
       </c>
-      <c r="E17" s="7" t="inlineStr">
+      <c r="F17" s="7" t="inlineStr">
         <is>
           <t>馬會書面批准 v1；每一版都有審批記錄；更新知識庫不用重新燒錄玩具</t>
         </is>
@@ -1543,12 +1614,17 @@
           <t>11/20</t>
         </is>
       </c>
-      <c r="D18" s="6" t="inlineStr">
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>我方軟件</t>
+        </is>
+      </c>
+      <c r="E18" s="6" t="inlineStr">
         <is>
           <t>管理功能</t>
         </is>
       </c>
-      <c r="E18" s="7" t="inlineStr">
+      <c r="F18" s="7" t="inlineStr">
         <is>
           <t>內容管理員：上載知識庫並送審、發佈角色；超級管理員：看設備最後上線、韌體版本、錯誤，發佈 OTA，解綁和換機；任何管理員都看不到對話內容</t>
         </is>
@@ -1566,12 +1642,17 @@
           <t>12/4</t>
         </is>
       </c>
-      <c r="D19" s="6" t="inlineStr">
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>我方軟件</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="inlineStr">
         <is>
           <t>三個品牌各自一套系統</t>
         </is>
       </c>
-      <c r="E19" s="7" t="inlineStr">
+      <c r="F19" s="7" t="inlineStr">
         <is>
           <t>三套各自上線，冒煙測試（登入、對話、OTA 檢查）通過；部署腳本一次跑完三套；一套停機不影響另外兩套</t>
         </is>
@@ -1593,12 +1674,17 @@
           <t>11/27</t>
         </is>
       </c>
-      <c r="D20" s="6" t="inlineStr">
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>我方全體</t>
+        </is>
+      </c>
+      <c r="E20" s="6" t="inlineStr">
         <is>
           <t>內部測試（20 台、4 週）</t>
         </is>
       </c>
-      <c r="E20" s="7" t="inlineStr">
+      <c r="F20" s="7" t="inlineStr">
         <is>
           <t>每週記錄對話輪數、首字延遲、每台成本、安全事件；第 4 週出測試報告</t>
         </is>
@@ -1616,12 +1702,17 @@
           <t>12/4</t>
         </is>
       </c>
-      <c r="D21" s="6" t="inlineStr">
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>我方軟件</t>
+        </is>
+      </c>
+      <c r="E21" s="6" t="inlineStr">
         <is>
           <t>系統測試</t>
         </is>
       </c>
-      <c r="E21" s="7" t="inlineStr">
+      <c r="F21" s="7" t="inlineStr">
         <is>
           <t>全流程測試通過；按 3,000 台規模壓測（150–300 個同時對話）通過；安全測試通過；嚴重問題 0 個</t>
         </is>
@@ -1643,12 +1734,17 @@
           <t>12/18</t>
         </is>
       </c>
-      <c r="D22" s="6" t="inlineStr">
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>馬會、政協青年聯會；我方</t>
+        </is>
+      </c>
+      <c r="E22" s="6" t="inlineStr">
         <is>
           <t>客戶 UAT（用試產機和正式版 App）</t>
         </is>
       </c>
-      <c r="E22" s="7" t="inlineStr">
+      <c r="F22" s="7" t="inlineStr">
         <is>
           <t>按 UAT 清單逐項測完；馬會、政協青年聯會書面簽收；嚴重問題 0 個，其他問題都有處理日期；3 位非團隊成員從開箱到第一次對話都在 10 分鐘內完成</t>
         </is>
@@ -1666,12 +1762,17 @@
           <t>1/8</t>
         </is>
       </c>
-      <c r="D23" s="6" t="inlineStr">
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>我方軟件</t>
+        </is>
+      </c>
+      <c r="E23" s="6" t="inlineStr">
         <is>
           <t>上線前最後確認</t>
         </is>
       </c>
-      <c r="E23" s="7" t="inlineStr">
+      <c r="F23" s="7" t="inlineStr">
         <is>
           <t>UAT 遺留問題全部處理；正式環境凍結，只修 bug；監控和告警正常</t>
         </is>
@@ -1679,12 +1780,12 @@
     </row>
   </sheetData>
   <mergeCells count="9">
+    <mergeCell ref="A2:F2"/>
     <mergeCell ref="A9:A12"/>
-    <mergeCell ref="A2:E2"/>
     <mergeCell ref="A22:A23"/>
     <mergeCell ref="A13:A14"/>
+    <mergeCell ref="A1:F1"/>
     <mergeCell ref="A15:A17"/>
-    <mergeCell ref="A1:E1"/>
     <mergeCell ref="A20:A21"/>
     <mergeCell ref="A5:A8"/>
     <mergeCell ref="A18:A19"/>
